--- a/ZenPro_v3_Signals.xlsx
+++ b/ZenPro_v3_Signals.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🇺🇸 US Markets" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📅 WM EMA Cross" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📈 Volume Spurt" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 52W &amp; ATH" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🏆 52W and ATH" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚀 RS Score" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💰 MF &amp; ETF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="💰 MF and ETF" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="🚀 IPO Signals" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 Ratios" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +48,34 @@
     </font>
     <font>
       <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="FFE8F5E9"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
       <color rgb="FF4CAF50"/>
-      <sz val="10"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="FF00E676"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="FFFFD60A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="FFE8F5E9"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="FF00AAFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Consolas"/>
@@ -65,6 +91,11 @@
     </font>
     <font>
       <name val="Consolas"/>
+      <color rgb="FF4CAF50"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
       <b val="1"/>
       <color rgb="FF00AAFF"/>
       <sz val="12"/>
@@ -73,6 +104,11 @@
       <name val="Consolas"/>
       <b val="1"/>
       <color rgb="FF00AAFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="FFFF2D55"/>
       <sz val="9"/>
     </font>
     <font>
@@ -119,6 +155,11 @@
     </font>
     <font>
       <name val="Consolas"/>
+      <color rgb="FFFF9500"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
       <b val="1"/>
       <color rgb="FF00E676"/>
       <sz val="10"/>
@@ -138,27 +179,6 @@
     <font>
       <name val="Consolas"/>
       <b val="1"/>
-      <color rgb="FFE8F5E9"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="FFFFD60A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="FFE8F5E9"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="FF4CAF50"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <b val="1"/>
       <color rgb="FFFF6B6B"/>
       <sz val="12"/>
     </font>
@@ -169,7 +189,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -183,7 +203,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF0D3320"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF071410"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF280A0E"/>
       </patternFill>
     </fill>
     <fill>
@@ -223,7 +253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -231,76 +261,154 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -669,24 +777,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚡ ZENPRO · BULLISH SIGNALS · 24 Mar 2026 · Above EMA200 Only</t>
+          <t>⚡ ZENPRO v3.2 · BULLISH · 24 Mar 2026 · Above EMA200</t>
         </is>
       </c>
     </row>
@@ -723,7 +831,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>VOL RATIO</t>
+          <t>VOL</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -733,21 +841,169 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>CHANGE%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>CHG%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>No signals today</t>
-        </is>
+          <t>CRAFTSMAN</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>🟢 EMA200↑</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>🐂BULL</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>6843</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>4.53</v>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>🟢 Sq10/20</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>🐂BULL</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>150.11</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>🟡 RSI/SMA↑</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>🐂BULL</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>2331.8</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>🟢 Sq10/20</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>🐂BULL</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>2331.8</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -760,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -771,36 +1027,335 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · RATIO CHARTS · Gold=2300 · DXY=104.00 · 24 Mar 2026</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · RATIOS · Gold=4366 DXY=99.46 · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>INDEX</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>INDEX/GOLD</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>INDEX/DXY</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>IDX/GOLD</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>IDX/DXY</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>CHG%</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>TREND</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="n">
+        <v>5.2478</v>
+      </c>
+      <c r="C3" s="31" t="n">
+        <v>230.37</v>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>+1.78%</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="n">
+        <v>12.0487</v>
+      </c>
+      <c r="C4" s="31" t="n">
+        <v>528.92</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>+2.27%</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY IT</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="n">
+        <v>6.7907</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>298.1</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>+1.72%</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY AUTO</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>5.6149</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>246.49</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>+2.43%</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY PHARMA</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>5.0937</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>223.61</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>+0.85%</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY FMCG</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="n">
+        <v>10.6292</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>466.61</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>+1.25%</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY METAL</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="n">
+        <v>2.533</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>111.19</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>+1.80%</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY REALTY</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>0.1544</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>+1.59%</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY ENERGY</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="n">
+        <v>8.0352</v>
+      </c>
+      <c r="C11" s="31" t="n">
+        <v>352.73</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>+0.70%</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY MEDIA</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>+3.45%</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>NIFTY INFRA</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>2.0005</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>87.81999999999999</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>+1.87%</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>PSU BANK</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>1.9142</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>84.03</v>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>+1.53%</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>MIDCAP 50</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>3.5299</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>154.96</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>+2.74%</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>▲UP</t>
         </is>
       </c>
     </row>
@@ -824,71 +1379,71 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · SELL / CAUTION SIGNALS · 24 Mar 2026</t>
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · SELL/CAUTION · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>SYMBOL</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>TF</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>DIRECTION</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>VOL RATIO</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>VOL</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>EMA200</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>CHANGE%</t>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>CHG%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>No signals today</t>
         </is>
@@ -910,85 +1465,194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · US MARKETS · 24 Mar 2026</t>
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · US MARKETS · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>SYMBOL</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>TF</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D2" s="13" t="inlineStr">
         <is>
           <t>DIRECTION</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F2" s="13" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>VOL RATIO</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>VOL</t>
+        </is>
+      </c>
+      <c r="H2" s="13" t="inlineStr">
         <is>
           <t>EMA200</t>
         </is>
       </c>
-      <c r="I2" s="7" t="inlineStr">
-        <is>
-          <t>CHANGE%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>CHG%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>No signals today</t>
-        </is>
+          <t>MRK</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>🟢 Sq10/20</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>🐂BULL</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>115.83</v>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>🟠 RSI/SMA↓</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>207.05</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>🔴 MACD 0↓</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>233.93</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H5" s="22" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1001,85 +1665,623 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · WEEKLY &amp; MONTHLY EMA CROSSES · 24 Mar 2026</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · W/M EMA CROSSES · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>SYMBOL</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>TF</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>DIRECTION</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
-        <is>
-          <t>VOL RATIO</t>
-        </is>
-      </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>VOL</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
         <is>
           <t>EMA200</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
-        <is>
-          <t>CHANGE%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>No signals today</t>
-        </is>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>CHG%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C3" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E10↓</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="n">
+        <v>1366.3</v>
+      </c>
+      <c r="F3" s="20" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G3" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="22" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I3" s="18" t="n">
+        <v>-5.82</v>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E20↓</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>1366.3</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>-5.82</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E10↓</t>
+        </is>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>1366.3</v>
+      </c>
+      <c r="F5" s="20" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>-11.87</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E10↓</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>480.95</v>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>-10.06</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C7" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E20↓</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>480.95</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="n">
+        <v>-10.06</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E10↓</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>8898</v>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>-10.77</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C9" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E10↓</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>3031.3</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>-10.78</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E20↓</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>3031.3</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>-10.78</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C11" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E20↓</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>886.4</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>-3.83</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E10↓</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>1418.9</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>-17.96</v>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C13" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E20↓</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>1418.9</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>-17.96</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E10↓</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>4126</v>
+      </c>
+      <c r="F14" s="20" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>-18.79</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E20↓</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="F15" s="20" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>-15.5</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>🔴 W/M E20↓</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>3899.5</v>
+      </c>
+      <c r="F16" s="20" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>-5.04</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1092,81 +2294,864 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · VOLUME SPURT · 24 Mar 2026</t>
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · VOLUME SPURT · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>SYMBOL</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>VOLUME</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>30D AVG</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>VOL RATIO</t>
-        </is>
-      </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="E2" s="27" t="inlineStr">
+        <is>
+          <t>RATIO</t>
+        </is>
+      </c>
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>EMA200</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="27" t="inlineStr">
         <is>
           <t>CHG%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>— VOLUME &gt; 30D AVERAGE —</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>— VOLUME &gt; 1 MILLION SHARES —</t>
-        </is>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>CHOLAHLDNG</t>
+        </is>
+      </c>
+      <c r="B4" s="30" t="n">
+        <v>1374.6</v>
+      </c>
+      <c r="C4" s="31" t="n">
+        <v>411208</v>
+      </c>
+      <c r="D4" s="32" t="n">
+        <v>201004</v>
+      </c>
+      <c r="E4" s="33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F4" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G4" s="35" t="n">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>DEEPAKFERT</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="n">
+        <v>921.05</v>
+      </c>
+      <c r="C5" s="31" t="n">
+        <v>509977</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>257655</v>
+      </c>
+      <c r="E5" s="33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="F5" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G5" s="35" t="n">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n">
+        <v>149.89</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>4832671</v>
+      </c>
+      <c r="D6" s="32" t="n">
+        <v>3123341</v>
+      </c>
+      <c r="E6" s="33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G6" s="35" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>291.25</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>33332205</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>21555899</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F7" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>398.75</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>12402671</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>8101137</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>3899.5</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>1300523</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>875649</v>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>1418.9</v>
+      </c>
+      <c r="C10" s="31" t="n">
+        <v>2457386</v>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>1740409</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G10" s="35" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>2331.8</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>1275794</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>913067</v>
+      </c>
+      <c r="E11" s="37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>8898</v>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>438085</v>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>315936</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G12" s="35" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>1334.3</v>
+      </c>
+      <c r="C13" s="31" t="n">
+        <v>249453</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>195236</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="n">
+        <v>608.1</v>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>633827</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>493687</v>
+      </c>
+      <c r="E14" s="33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G14" s="34" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>MANYAVAR</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="C15" s="31" t="n">
+        <v>601265</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>490102</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>3031.3</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>3943843</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>3267116</v>
+      </c>
+      <c r="E16" s="33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="C17" s="31" t="n">
+        <v>8841890</v>
+      </c>
+      <c r="D17" s="32" t="n">
+        <v>7410275</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G17" s="35" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>2116.8</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>747214</v>
+      </c>
+      <c r="D18" s="32" t="n">
+        <v>636974</v>
+      </c>
+      <c r="E18" s="33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>604.05</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>2989995</v>
+      </c>
+      <c r="D19" s="32" t="n">
+        <v>2611321</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>— VOLUME &gt; 1 MILLION —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>291.25</v>
+      </c>
+      <c r="C22" s="31" t="n">
+        <v>33332205</v>
+      </c>
+      <c r="D22" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G22" s="35" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>24088358</v>
+      </c>
+      <c r="D23" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="n">
+        <v>150.11</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>21759041</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="37" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="n">
+        <v>398.75</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>12402671</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="C26" s="31" t="n">
+        <v>8841890</v>
+      </c>
+      <c r="D26" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G26" s="35" t="n">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="29" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="n">
+        <v>149.89</v>
+      </c>
+      <c r="C27" s="31" t="n">
+        <v>4832671</v>
+      </c>
+      <c r="D27" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="33" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="29" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B28" s="30" t="n">
+        <v>3031.3</v>
+      </c>
+      <c r="C28" s="31" t="n">
+        <v>3943843</v>
+      </c>
+      <c r="D28" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G28" s="35" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="n">
+        <v>604.05</v>
+      </c>
+      <c r="C29" s="31" t="n">
+        <v>2989995</v>
+      </c>
+      <c r="D29" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="33" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G29" s="35" t="n">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>2901874</v>
+      </c>
+      <c r="D30" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="33" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G30" s="35" t="n">
+        <v>2.48</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="29" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="n">
+        <v>1418.9</v>
+      </c>
+      <c r="C31" s="31" t="n">
+        <v>2457386</v>
+      </c>
+      <c r="D31" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G31" s="35" t="n">
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="29" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="n">
+        <v>448.6</v>
+      </c>
+      <c r="C32" s="31" t="n">
+        <v>2152059</v>
+      </c>
+      <c r="D32" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="33" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G32" s="35" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="n">
+        <v>3899.5</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1300523</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="37" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="n">
+        <v>2331.8</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1275794</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1179,7 +3164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1191,71 +3176,311 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · 52W HIGH · ATH · 25% BELOW ATH · 24 Mar 2026</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · 52W/ATH · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>SYMBOL</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
         <is>
           <t>52W HIGH</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="24" t="inlineStr">
         <is>
           <t>ATH</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="24" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>EMA200</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>— AT / NEAR 52-WEEK HIGH —</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>— AT/NEAR 52-WEEK HIGH —</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B4" s="36" t="n">
+        <v>2331.8</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>2377.6</v>
+      </c>
+      <c r="D4" s="40" t="n">
+        <v>2381.29</v>
+      </c>
+      <c r="E4" s="37" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>— ALL-TIME HIGH —</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>— WITHIN 25% OF ALL-TIME HIGH (BUY ZONE) —</t>
+    <row r="8">
+      <c r="A8" s="42" t="inlineStr">
+        <is>
+          <t>— WITHIN 25% OF ATH (BUY ZONE) —</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>CRAFTSMAN</t>
+        </is>
+      </c>
+      <c r="B9" s="36" t="n">
+        <v>6843</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>8220</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>8119</v>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n">
+        <v>4126</v>
+      </c>
+      <c r="C10" s="35" t="n">
+        <v>5303</v>
+      </c>
+      <c r="D10" s="43" t="n">
+        <v>5206</v>
+      </c>
+      <c r="E10" s="33" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="F10" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>3899.5</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>4378.4</v>
+      </c>
+      <c r="D11" s="40" t="n">
+        <v>4342.6</v>
+      </c>
+      <c r="E11" s="37" t="n">
+        <v>36.1</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>CEATLTD</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="n">
+        <v>3451.7</v>
+      </c>
+      <c r="C12" s="35" t="n">
+        <v>4438</v>
+      </c>
+      <c r="D12" s="43" t="n">
+        <v>4302.7</v>
+      </c>
+      <c r="E12" s="33" t="n">
+        <v>45.3</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="n">
+        <v>3031.3</v>
+      </c>
+      <c r="C13" s="35" t="n">
+        <v>3839.9</v>
+      </c>
+      <c r="D13" s="43" t="n">
+        <v>3802.4</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="F13" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B14" s="36" t="n">
+        <v>2331.8</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2377.6</v>
+      </c>
+      <c r="D14" s="40" t="n">
+        <v>2381.29</v>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="n">
+        <v>1418.9</v>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>1831.5</v>
+      </c>
+      <c r="D15" s="43" t="n">
+        <v>1804.05</v>
+      </c>
+      <c r="E15" s="33" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="n">
+        <v>398.75</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>444.1</v>
+      </c>
+      <c r="D16" s="40" t="n">
+        <v>527.75</v>
+      </c>
+      <c r="E16" s="37" t="n">
+        <v>47.8</v>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="n">
+        <v>150.11</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>182.7</v>
+      </c>
+      <c r="D17" s="40" t="n">
+        <v>174.9</v>
+      </c>
+      <c r="E17" s="37" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1268,7 +3493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1280,48 +3505,768 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · RELATIVE STRENGTH SCORE · 24 Mar 2026</t>
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · RS SCORE · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>RANK</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="45" t="inlineStr">
         <is>
           <t>SYMBOL</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="45" t="inlineStr">
         <is>
           <t>RS SCORE</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="45" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
-        <is>
-          <t>CHANGE%</t>
-        </is>
-      </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="E2" s="45" t="inlineStr">
+        <is>
+          <t>CHG%</t>
+        </is>
+      </c>
+      <c r="F2" s="45" t="inlineStr">
         <is>
           <t>EMA200</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>— INDIA RS LEADERS (vs Nifty) —</t>
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>— INDIA RS LEADERS —</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="D4" s="36" t="n">
+        <v>150.11</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>CRAFTSMAN</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>6843</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>CEATLTD</t>
+        </is>
+      </c>
+      <c r="C6" s="35" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>3451.7</v>
+      </c>
+      <c r="E6" s="35" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F6" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>74.2</v>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>3899.5</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>73.2</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>4126</v>
+      </c>
+      <c r="E8" s="35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F8" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C9" s="30" t="n">
+        <v>67</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>8898</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F9" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="D10" s="36" t="n">
+        <v>2331.8</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="n">
+        <v>62.4</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>62.09</v>
+      </c>
+      <c r="E11" s="35" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="F11" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="29" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="C12" s="30" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>3031.3</v>
+      </c>
+      <c r="E12" s="35" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F12" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n">
+        <v>54.9</v>
+      </c>
+      <c r="D13" s="36" t="n">
+        <v>398.75</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>ZYDUSLIFE</t>
+        </is>
+      </c>
+      <c r="C14" s="30" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="D14" s="30" t="n">
+        <v>886.4</v>
+      </c>
+      <c r="E14" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="29" t="inlineStr">
+        <is>
+          <t>TORNTPOWER</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="D15" s="30" t="n">
+        <v>1366.3</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F15" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>ELGIEQUIP</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>480.95</v>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="F16" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>GODFRYPHLP</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D17" s="30" t="n">
+        <v>1897.5</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F17" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="29" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D18" s="30" t="n">
+        <v>2116.8</v>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F18" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>1418.9</v>
+      </c>
+      <c r="E19" s="35" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="F19" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="29" t="inlineStr">
+        <is>
+          <t>ISGEC</t>
+        </is>
+      </c>
+      <c r="C20" s="34" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="D20" s="30" t="n">
+        <v>882.7</v>
+      </c>
+      <c r="E20" s="34" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="29" t="inlineStr">
+        <is>
+          <t>DEEPAKFERT</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>921.05</v>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="F21" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>CHOLAHLDNG</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>1374.6</v>
+      </c>
+      <c r="E22" s="35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="F22" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="29" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="n">
+        <v>38.3</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>371.7</v>
+      </c>
+      <c r="E23" s="35" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="F23" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>IGL</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="D24" s="30" t="n">
+        <v>149.89</v>
+      </c>
+      <c r="E24" s="35" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="F24" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="n">
+        <v>36</v>
+      </c>
+      <c r="D25" s="30" t="n">
+        <v>320.8</v>
+      </c>
+      <c r="E25" s="35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="F25" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="29" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="D26" s="30" t="n">
+        <v>291.25</v>
+      </c>
+      <c r="E26" s="35" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F26" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D27" s="30" t="n">
+        <v>604.05</v>
+      </c>
+      <c r="E27" s="35" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F27" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="29" t="inlineStr">
+        <is>
+          <t>TATACHEM</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="D28" s="30" t="n">
+        <v>608.1</v>
+      </c>
+      <c r="E28" s="34" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F28" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="D29" s="30" t="n">
+        <v>1540.5</v>
+      </c>
+      <c r="E29" s="35" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="29" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D30" s="30" t="n">
+        <v>1334.3</v>
+      </c>
+      <c r="E30" s="35" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F30" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="29" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D31" s="30" t="n">
+        <v>448.6</v>
+      </c>
+      <c r="E31" s="35" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="F31" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>BRIGADE</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="D32" s="30" t="n">
+        <v>645.4</v>
+      </c>
+      <c r="E32" s="35" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="F32" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="29" t="inlineStr">
+        <is>
+          <t>MANYAVAR</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D33" s="30" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="E33" s="35" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F33" s="34" t="inlineStr">
+        <is>
+          <t>BELOW</t>
         </is>
       </c>
     </row>
@@ -1341,7 +4286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -1349,127 +4294,570 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · MUTUAL FUNDS &amp; ETFs · 10Y CAGR · 24 Mar 2026</t>
+      <c r="A1" s="23" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · MF + ETF · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>FUND NAME</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>NAV</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>1Y CAGR</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>3Y CAGR</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>5Y CAGR</t>
-        </is>
-      </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
         <is>
           <t>10Y CAGR</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="24" t="inlineStr">
         <is>
           <t>CATEGORY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>— TOP EQUITY MUTUAL FUNDS BY 10Y CAGR —</t>
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>— TOP EQUITY MFs BY 10Y CAGR —</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>Axis Small Cap Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B4" s="46" t="n">
+        <v>111.17</v>
+      </c>
+      <c r="C4" s="47" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="D4" s="47" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="E4" s="47" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F4" s="48" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="G4" s="49" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Small Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>Kotak Midcap Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n">
+        <v>146.76</v>
+      </c>
+      <c r="C5" s="47" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="D5" s="47" t="n">
+        <v>21</v>
+      </c>
+      <c r="E5" s="47" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="F5" s="48" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="G5" s="49" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Mid Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>quant Small Cap Fund - Growth Option - Direct Plan</t>
+        </is>
+      </c>
+      <c r="B6" s="46" t="n">
+        <v>248.64</v>
+      </c>
+      <c r="C6" s="47" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="D6" s="47" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>24.55</v>
+      </c>
+      <c r="F6" s="48" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="G6" s="49" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Small Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>Mirae Asset ELSS Tax Saver Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B7" s="46" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="C7" s="47" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D7" s="47" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="E7" s="47" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="F7" s="48" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="G7" s="49" t="inlineStr">
+        <is>
+          <t>Equity Scheme - ELSS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>Parag Parikh Flexi Cap Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B8" s="46" t="n">
+        <v>87.79000000000001</v>
+      </c>
+      <c r="C8" s="47" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="D8" s="47" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="E8" s="47" t="n">
+        <v>17.42</v>
+      </c>
+      <c r="F8" s="48" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="G8" s="49" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Flexi Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Equity &amp; Debt Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="n">
+        <v>428.58</v>
+      </c>
+      <c r="C9" s="47" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="D9" s="47" t="n">
+        <v>18.45</v>
+      </c>
+      <c r="E9" s="47" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="F9" s="48" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="G9" s="49" t="inlineStr">
+        <is>
+          <t>Hybrid Scheme - Aggressive Hybrid Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>ICICI Prudential Large Cap Fund (erstwhile Bluechip Fund)  - Growth</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n">
+        <v>103.05</v>
+      </c>
+      <c r="C10" s="47" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="D10" s="47" t="n">
+        <v>15.86</v>
+      </c>
+      <c r="E10" s="47" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="F10" s="46" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="G10" s="49" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Large Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>CANARA ROBECO EQUITY HYBRID FUND - DIRECT PLAN - GROWTH OPTION</t>
+        </is>
+      </c>
+      <c r="B11" s="46" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="C11" s="47" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="D11" s="47" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="E11" s="47" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F11" s="46" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="G11" s="49" t="inlineStr">
+        <is>
+          <t>Hybrid Scheme - Aggressive Hybrid Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>UTI Nifty 50 Index Fund - Growth Option- Direct</t>
+        </is>
+      </c>
+      <c r="B12" s="46" t="n">
+        <v>161.61</v>
+      </c>
+      <c r="C12" s="47" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="D12" s="47" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="E12" s="47" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="F12" s="46" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="G12" s="49" t="inlineStr">
+        <is>
+          <t>Other Scheme - Index Funds</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taurus Flexi Cap Fund - Regular Plan - Growth </t>
+        </is>
+      </c>
+      <c r="B13" s="46" t="n">
+        <v>205.26</v>
+      </c>
+      <c r="C13" s="47" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="D13" s="47" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="E13" s="47" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="F13" s="47" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="G13" s="49" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Flexi Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>SBI OVERNIGHT FUND - REGULAR PLAN - GROWTH</t>
         </is>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B14" s="46" t="n">
         <v>4315.03</v>
       </c>
-      <c r="C4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="C14" s="47" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="D14" s="47" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="E14" s="47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F14" s="47" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="G14" s="49" t="inlineStr">
         <is>
           <t>Debt Scheme - Overnight Fund</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>Franklin India Ultra Short Bond Fund - Super Institutional Plan - Direct - Growth</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="n">
-        <v>34.24</v>
-      </c>
-      <c r="C5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="23" t="inlineStr">
-        <is>
-          <t>Debt Scheme - Ultra Short Duration Fund</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="50" t="inlineStr">
         <is>
           <t>— ETFs &amp; BeES —</t>
         </is>
       </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Nifty BeES</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="n">
+        <v>259.83</v>
+      </c>
+      <c r="C17" s="33" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="D17" s="33" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="E17" s="33" t="n">
+        <v>68.87</v>
+      </c>
+      <c r="F17" s="33" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>Bank BeES</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="n">
+        <v>543.04</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="D18" s="33" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="E18" s="33" t="n">
+        <v>63.06</v>
+      </c>
+      <c r="F18" s="33" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Gold BeES</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="n">
+        <v>115.49</v>
+      </c>
+      <c r="C19" s="33" t="n">
+        <v>57.07</v>
+      </c>
+      <c r="D19" s="33" t="n">
+        <v>143.6</v>
+      </c>
+      <c r="E19" s="33" t="n">
+        <v>196.97</v>
+      </c>
+      <c r="F19" s="33" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>Silver BeES</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="n">
+        <v>212.31</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>120.06</v>
+      </c>
+      <c r="D20" s="33" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="E20" s="33" t="n">
+        <v>243.71</v>
+      </c>
+      <c r="F20" s="33" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>IT BeES</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="C21" s="33" t="n">
+        <v>-16.98</v>
+      </c>
+      <c r="D21" s="33" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E21" s="33" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F21" s="33" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>Junior BeES</t>
+        </is>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>672.29</v>
+      </c>
+      <c r="C22" s="33" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D22" s="33" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="E22" s="33" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="F22" s="33" t="inlineStr"/>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>SBI Nifty ETF</t>
+        </is>
+      </c>
+      <c r="B23" s="30" t="n">
+        <v>245.18</v>
+      </c>
+      <c r="C23" s="33" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="D23" s="33" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="E23" s="33" t="n">
+        <v>68.17</v>
+      </c>
+      <c r="F23" s="33" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>Momentum 100</t>
+        </is>
+      </c>
+      <c r="B24" s="30" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="C24" s="33" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D24" s="33" t="n">
+        <v>83.67</v>
+      </c>
+      <c r="E24" s="33" t="n">
+        <v>136.78</v>
+      </c>
+      <c r="F24" s="33" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>Hang Seng BeES</t>
+        </is>
+      </c>
+      <c r="B25" s="30" t="n">
+        <v>461.13</v>
+      </c>
+      <c r="C25" s="33" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="D25" s="33" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="E25" s="33" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="F25" s="33" t="inlineStr"/>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="29" t="inlineStr">
+        <is>
+          <t>Bharat Bond 2032</t>
+        </is>
+      </c>
+      <c r="B26" s="30" t="n">
+        <v>114.47</v>
+      </c>
+      <c r="C26" s="33" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="D26" s="33" t="n">
+        <v>97.16</v>
+      </c>
+      <c r="E26" s="33" t="n">
+        <v>226.96</v>
+      </c>
+      <c r="F26" s="33" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1482,65 +4870,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
-        <is>
-          <t>⚡ ZENPRO · IPO STOCKS — BULLISH SIGNALS · 24 Mar 2026</t>
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>⚡ ZENPRO v3.2 · IPO BULLISH · 24 Mar 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="52" t="inlineStr">
         <is>
           <t>SYMBOL</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
-        <is>
-          <t>AGE GROUP</t>
-        </is>
-      </c>
-      <c r="C2" s="26" t="inlineStr">
+      <c r="B2" s="52" t="inlineStr">
+        <is>
+          <t>AGE</t>
+        </is>
+      </c>
+      <c r="C2" s="52" t="inlineStr">
         <is>
           <t>SIGNAL</t>
         </is>
       </c>
-      <c r="D2" s="26" t="inlineStr">
+      <c r="D2" s="52" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="E2" s="26" t="inlineStr">
+      <c r="E2" s="52" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="F2" s="26" t="inlineStr">
+      <c r="F2" s="52" t="inlineStr">
         <is>
           <t>EMA200</t>
         </is>
       </c>
-      <c r="G2" s="26" t="inlineStr">
-        <is>
-          <t>VOL RATIO</t>
-        </is>
-      </c>
-      <c r="H2" s="26" t="inlineStr">
-        <is>
-          <t>DIRECTION</t>
+      <c r="G2" s="52" t="inlineStr">
+        <is>
+          <t>VOL</t>
+        </is>
+      </c>
+      <c r="H2" s="52" t="inlineStr">
+        <is>
+          <t>DIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>DELHIVERY</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>🟢 EMA200↑</t>
+        </is>
+      </c>
+      <c r="D3" s="36" t="n">
+        <v>418.9</v>
+      </c>
+      <c r="E3" s="37" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>🟡 RSI/SMA↑</t>
+        </is>
+      </c>
+      <c r="D4" s="36" t="n">
+        <v>240.05</v>
+      </c>
+      <c r="E4" s="37" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>NYKAA</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>🟢 EMA200↑</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>240.05</v>
+      </c>
+      <c r="E5" s="37" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>MEDPLUS</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>🟢 EMA200↑</t>
+        </is>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>822.15</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>CRAFTSMAN</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>🟢 EMA200↑</t>
+        </is>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>6843</v>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>🟢 EMA200↑</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>877.5</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
     </row>

--- a/ZenPro_v3_Signals.xlsx
+++ b/ZenPro_v3_Signals.xlsx
@@ -909,7 +909,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>⚡ ZENPRO v3.2 · RATIOS · Gold=4388 DXY=99.40 · 24 Mar 2026</t>
+          <t>⚡ ZENPRO v3.2 · RATIOS · Gold=4401 DXY=99.33 · 24 Mar 2026</t>
         </is>
       </c>
     </row>
@@ -947,10 +947,10 @@
         </is>
       </c>
       <c r="B3" s="29" t="n">
-        <v>5.2217</v>
+        <v>5.2065</v>
       </c>
       <c r="C3" s="30" t="n">
-        <v>230.51</v>
+        <v>230.66</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
@@ -970,10 +970,10 @@
         </is>
       </c>
       <c r="B4" s="29" t="n">
-        <v>11.9888</v>
+        <v>11.9539</v>
       </c>
       <c r="C4" s="30" t="n">
-        <v>529.24</v>
+        <v>529.59</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="B5" s="29" t="n">
-        <v>6.757</v>
+        <v>6.7373</v>
       </c>
       <c r="C5" s="30" t="n">
-        <v>298.28</v>
+        <v>298.48</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
@@ -1016,10 +1016,10 @@
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>5.587</v>
+        <v>5.5708</v>
       </c>
       <c r="C6" s="30" t="n">
-        <v>246.63</v>
+        <v>246.8</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>5.0684</v>
+        <v>5.0537</v>
       </c>
       <c r="C7" s="30" t="n">
-        <v>223.74</v>
+        <v>223.89</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>10.5764</v>
+        <v>10.5457</v>
       </c>
       <c r="C8" s="30" t="n">
-        <v>466.89</v>
+        <v>467.2</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
@@ -1085,10 +1085,10 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>2.5204</v>
+        <v>2.513</v>
       </c>
       <c r="C9" s="30" t="n">
-        <v>111.26</v>
+        <v>111.34</v>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>0.1536</v>
+        <v>0.1531</v>
       </c>
       <c r="C10" s="30" t="n">
         <v>6.78</v>
@@ -1131,10 +1131,10 @@
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>7.9953</v>
+        <v>7.972</v>
       </c>
       <c r="C11" s="30" t="n">
-        <v>352.95</v>
+        <v>353.18</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>0.2955</v>
+        <v>0.2946</v>
       </c>
       <c r="C12" s="30" t="n">
-        <v>13.04</v>
+        <v>13.05</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>1.9905</v>
+        <v>1.9847</v>
       </c>
       <c r="C13" s="30" t="n">
-        <v>87.87</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>1.9047</v>
+        <v>1.8991</v>
       </c>
       <c r="C14" s="30" t="n">
-        <v>84.08</v>
+        <v>84.14</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>3.5123</v>
+        <v>3.5021</v>
       </c>
       <c r="C15" s="30" t="n">
-        <v>155.05</v>
+        <v>155.15</v>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1435,13 +1435,13 @@
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>116.46</v>
+        <v>115.71</v>
       </c>
       <c r="F3" s="7" t="n">
-        <v>51.7</v>
+        <v>49.1</v>
       </c>
       <c r="G3" s="8" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
@@ -1449,52 +1449,52 @@
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.68</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>MRK</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>🟢 Sq20/50</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>🐂BULL</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>116.46</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>🟣 MACD↓</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>🐻BEAR</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>296.41</v>
+      </c>
+      <c r="F4" s="20" t="n">
+        <v>37.8</v>
+      </c>
+      <c r="G4" s="21" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H4" s="22" t="inlineStr">
         <is>
           <t>ABOVE</t>
         </is>
       </c>
-      <c r="I4" s="5" t="n">
-        <v>0.68</v>
+      <c r="I4" s="18" t="n">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B5" s="16" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>🟣 MACD↓</t>
+          <t>🟠 RSI/SMA↓</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
@@ -1513,27 +1513,27 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>296.47</v>
+        <v>207.85</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>37.9</v>
+        <v>44.5</v>
       </c>
       <c r="G5" s="21" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
-        <is>
-          <t>ABOVE</t>
+        <v>0.12</v>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>BELOW</t>
         </is>
       </c>
       <c r="I5" s="18" t="n">
-        <v>-1.85</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>🟠 RSI/SMA↓</t>
+          <t>🔴 MACD 0↓</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
@@ -1552,60 +1552,21 @@
         </is>
       </c>
       <c r="E6" s="19" t="n">
-        <v>207.55</v>
+        <v>234.46</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>44.2</v>
+        <v>40.8</v>
       </c>
       <c r="G6" s="21" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H6" s="18" t="inlineStr">
-        <is>
-          <t>BELOW</t>
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="22" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
         </is>
       </c>
       <c r="I6" s="18" t="n">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>🔴 MACD 0↓</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>🐻BEAR</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>235.32</v>
-      </c>
-      <c r="F7" s="20" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>ABOVE</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="n">
-        <v>-0.04</v>
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -1714,7 +1675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2325,76 +2286,76 @@
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="B26" s="29" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>8123440</v>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="35" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="F26" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G26" s="34" t="n">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="B26" s="36" t="n">
+      <c r="B27" s="36" t="n">
         <v>262.5</v>
       </c>
-      <c r="C26" s="14" t="n">
+      <c r="C27" s="14" t="n">
         <v>6879978</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="37" t="n">
+      <c r="E27" s="37" t="n">
         <v>0.8100000000000001</v>
       </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>ABOVE</t>
         </is>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G27" s="5" t="n">
         <v>3.2</v>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-      <c r="B27" s="29" t="n">
-        <v>604.05</v>
-      </c>
-      <c r="C27" s="30" t="n">
-        <v>2989995</v>
-      </c>
-      <c r="D27" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="35" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="F27" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
-        </is>
-      </c>
-      <c r="G27" s="34" t="n">
-        <v>3.71</v>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="28" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B28" s="29" t="n">
-        <v>433.1</v>
+        <v>604.05</v>
       </c>
       <c r="C28" s="30" t="n">
-        <v>2423789</v>
+        <v>2989995</v>
       </c>
       <c r="D28" s="31" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="35" t="n">
-        <v>1.65</v>
+        <v>1.15</v>
       </c>
       <c r="F28" s="33" t="inlineStr">
         <is>
@@ -2402,26 +2363,26 @@
         </is>
       </c>
       <c r="G28" s="34" t="n">
-        <v>2.21</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="28" t="inlineStr">
         <is>
-          <t>AVANTEL</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B29" s="29" t="n">
-        <v>121.03</v>
+        <v>433.1</v>
       </c>
       <c r="C29" s="30" t="n">
-        <v>1810186</v>
+        <v>2423789</v>
       </c>
       <c r="D29" s="31" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="35" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="F29" s="33" t="inlineStr">
         <is>
@@ -2429,26 +2390,26 @@
         </is>
       </c>
       <c r="G29" s="34" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="B30" s="29" t="n">
-        <v>1583.5</v>
+        <v>121.03</v>
       </c>
       <c r="C30" s="30" t="n">
-        <v>1556964</v>
+        <v>1810186</v>
       </c>
       <c r="D30" s="31" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="35" t="n">
-        <v>1.74</v>
+        <v>1.51</v>
       </c>
       <c r="F30" s="33" t="inlineStr">
         <is>
@@ -2456,26 +2417,26 @@
         </is>
       </c>
       <c r="G30" s="34" t="n">
-        <v>1.02</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B31" s="29" t="n">
-        <v>2471.6</v>
+        <v>1583.5</v>
       </c>
       <c r="C31" s="30" t="n">
-        <v>1285209</v>
+        <v>1556964</v>
       </c>
       <c r="D31" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="E31" s="32" t="n">
-        <v>2.43</v>
+      <c r="E31" s="35" t="n">
+        <v>1.74</v>
       </c>
       <c r="F31" s="33" t="inlineStr">
         <is>
@@ -2483,33 +2444,60 @@
         </is>
       </c>
       <c r="G31" s="34" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B32" s="29" t="n">
-        <v>118</v>
+        <v>2471.6</v>
       </c>
       <c r="C32" s="30" t="n">
-        <v>1161733</v>
+        <v>1285209</v>
       </c>
       <c r="D32" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="E32" s="35" t="n">
+      <c r="E32" s="32" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="F32" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G32" s="34" t="n">
+        <v>3.35</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>LXCHEM</t>
+        </is>
+      </c>
+      <c r="B33" s="29" t="n">
+        <v>118</v>
+      </c>
+      <c r="C33" s="30" t="n">
+        <v>1161733</v>
+      </c>
+      <c r="D33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="35" t="n">
         <v>1.45</v>
       </c>
-      <c r="F32" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
-        </is>
-      </c>
-      <c r="G32" s="34" t="n">
+      <c r="F33" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+      <c r="G33" s="34" t="n">
         <v>4.52</v>
       </c>
     </row>
@@ -2530,7 +2518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2604,68 +2592,68 @@
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="n">
+        <v>6184.5</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>6965</v>
+      </c>
+      <c r="D8" s="42" t="n">
+        <v>6649.5</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>THANGAMAYL</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B9" s="36" t="n">
         <v>3309.4</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C9" s="5" t="n">
         <v>4149</v>
       </c>
-      <c r="D8" s="42" t="n">
+      <c r="D9" s="42" t="n">
         <v>3959.2</v>
       </c>
-      <c r="E8" s="37" t="n">
+      <c r="E9" s="37" t="n">
         <v>41.7</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>ABOVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>SRF</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>2471.6</v>
-      </c>
-      <c r="C9" s="34" t="n">
-        <v>3325</v>
-      </c>
-      <c r="D9" s="32" t="n">
-        <v>3276.15</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>42.3</v>
-      </c>
-      <c r="F9" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>1583.5</v>
+        <v>2471.6</v>
       </c>
       <c r="C10" s="34" t="n">
-        <v>1892.5</v>
+        <v>3325</v>
       </c>
       <c r="D10" s="32" t="n">
-        <v>1870</v>
+        <v>3276.15</v>
       </c>
       <c r="E10" s="35" t="n">
-        <v>33.4</v>
+        <v>42.3</v>
       </c>
       <c r="F10" s="33" t="inlineStr">
         <is>
@@ -2674,72 +2662,168 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>1411.8</v>
-      </c>
-      <c r="C11" s="34" t="n">
-        <v>1611.8</v>
-      </c>
-      <c r="D11" s="32" t="n">
-        <v>1592.3</v>
-      </c>
-      <c r="E11" s="35" t="n">
-        <v>50.9</v>
-      </c>
-      <c r="F11" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="B11" s="36" t="n">
+        <v>2095.7</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>2297.9</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <v>2272.7</v>
+      </c>
+      <c r="E11" s="37" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="28" t="inlineStr">
         <is>
+          <t>MFSL</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>1583.5</v>
+      </c>
+      <c r="C12" s="34" t="n">
+        <v>1892.5</v>
+      </c>
+      <c r="D12" s="32" t="n">
+        <v>1870</v>
+      </c>
+      <c r="E12" s="35" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="n">
+        <v>1411.8</v>
+      </c>
+      <c r="C13" s="34" t="n">
+        <v>1611.8</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>1592.3</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="n">
+        <v>802.2</v>
+      </c>
+      <c r="C14" s="34" t="n">
+        <v>994</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <v>965.75</v>
+      </c>
+      <c r="E14" s="35" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
           <t>KIMS</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B15" s="29" t="n">
         <v>631.05</v>
       </c>
-      <c r="C12" s="34" t="n">
+      <c r="C15" s="34" t="n">
         <v>798.4</v>
       </c>
-      <c r="D12" s="32" t="n">
+      <c r="D15" s="32" t="n">
         <v>789.35</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E15" s="35" t="n">
         <v>39.1</v>
       </c>
-      <c r="F12" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="B16" s="29" t="n">
+        <v>570.85</v>
+      </c>
+      <c r="C16" s="34" t="n">
+        <v>747</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <v>730.15</v>
+      </c>
+      <c r="E16" s="35" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B17" s="36" t="n">
         <v>262.5</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C17" s="5" t="n">
         <v>302</v>
       </c>
-      <c r="D13" s="42" t="n">
+      <c r="D17" s="42" t="n">
         <v>299.85</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E17" s="37" t="n">
         <v>40.4</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>ABOVE</t>
         </is>
@@ -2763,7 +2847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2845,98 +2929,98 @@
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="31" t="n">
+      <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="28" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>NAVINFLUOR</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>92.40000000000001</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>6184.5</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>MFSL</t>
         </is>
       </c>
-      <c r="C5" s="34" t="n">
+      <c r="C6" s="34" t="n">
         <v>87.5</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D6" s="29" t="n">
         <v>1583.5</v>
       </c>
-      <c r="E5" s="34" t="n">
+      <c r="E6" s="34" t="n">
         <v>1.02</v>
       </c>
-      <c r="F5" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>FEDERALBNK</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C7" s="5" t="n">
         <v>86</v>
       </c>
-      <c r="D6" s="36" t="n">
+      <c r="D7" s="36" t="n">
         <v>262.5</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E7" s="5" t="n">
         <v>3.2</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>ABOVE</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="28" t="inlineStr">
-        <is>
-          <t>SURYODAY</t>
-        </is>
-      </c>
-      <c r="C7" s="34" t="n">
-        <v>70</v>
-      </c>
-      <c r="D7" s="29" t="n">
-        <v>125.53</v>
-      </c>
-      <c r="E7" s="34" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="F7" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
-        </is>
-      </c>
-    </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="31" t="n">
+      <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="C8" s="29" t="n">
-        <v>63.4</v>
-      </c>
-      <c r="D8" s="29" t="n">
-        <v>1411.8</v>
-      </c>
-      <c r="E8" s="34" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="F8" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>GLENMARK</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>2095.7</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
         </is>
       </c>
     </row>
@@ -2946,17 +3030,17 @@
       </c>
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>RATEGAIN</t>
-        </is>
-      </c>
-      <c r="C9" s="29" t="n">
-        <v>61.2</v>
+          <t>GRAPHITE</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="n">
+        <v>73.5</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>480.85</v>
+        <v>570.85</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>3.02</v>
+        <v>1.27</v>
       </c>
       <c r="F9" s="33" t="inlineStr">
         <is>
@@ -2970,17 +3054,17 @@
       </c>
       <c r="B10" s="28" t="inlineStr">
         <is>
-          <t>METROPOLIS</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>60</v>
+          <t>SURYODAY</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="n">
+        <v>70</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>443</v>
-      </c>
-      <c r="E10" s="33" t="n">
-        <v>-1.6</v>
+        <v>125.53</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>0.13</v>
       </c>
       <c r="F10" s="33" t="inlineStr">
         <is>
@@ -2994,17 +3078,17 @@
       </c>
       <c r="B11" s="28" t="inlineStr">
         <is>
-          <t>AVANTEL</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="C11" s="29" t="n">
-        <v>58.2</v>
+        <v>63.4</v>
       </c>
       <c r="D11" s="29" t="n">
-        <v>121.03</v>
+        <v>1411.8</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>2.32</v>
+        <v>0.28</v>
       </c>
       <c r="F11" s="33" t="inlineStr">
         <is>
@@ -3018,17 +3102,17 @@
       </c>
       <c r="B12" s="28" t="inlineStr">
         <is>
-          <t>KIMS</t>
+          <t>RATEGAIN</t>
         </is>
       </c>
       <c r="C12" s="29" t="n">
-        <v>58</v>
+        <v>61.2</v>
       </c>
       <c r="D12" s="29" t="n">
-        <v>631.05</v>
+        <v>480.85</v>
       </c>
       <c r="E12" s="34" t="n">
-        <v>0.09</v>
+        <v>3.02</v>
       </c>
       <c r="F12" s="33" t="inlineStr">
         <is>
@@ -3037,26 +3121,26 @@
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="4" t="n">
+      <c r="A13" s="31" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>AARTIIND</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>418.7</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>ABOVE</t>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>METROPOLIS</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>443</v>
+      </c>
+      <c r="E13" s="33" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
         </is>
       </c>
     </row>
@@ -3066,17 +3150,17 @@
       </c>
       <c r="B14" s="28" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>AVANTEL</t>
         </is>
       </c>
       <c r="C14" s="29" t="n">
-        <v>50.7</v>
+        <v>58.2</v>
       </c>
       <c r="D14" s="29" t="n">
-        <v>3756.5</v>
+        <v>121.03</v>
       </c>
       <c r="E14" s="34" t="n">
-        <v>2.76</v>
+        <v>2.32</v>
       </c>
       <c r="F14" s="33" t="inlineStr">
         <is>
@@ -3090,17 +3174,17 @@
       </c>
       <c r="B15" s="28" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
-        </is>
-      </c>
-      <c r="C15" s="33" t="n">
-        <v>49.5</v>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>58.2</v>
       </c>
       <c r="D15" s="29" t="n">
-        <v>1366.3</v>
+        <v>149.99</v>
       </c>
       <c r="E15" s="34" t="n">
-        <v>0.26</v>
+        <v>1.11</v>
       </c>
       <c r="F15" s="33" t="inlineStr">
         <is>
@@ -3114,17 +3198,17 @@
       </c>
       <c r="B16" s="28" t="inlineStr">
         <is>
-          <t>KOLTEPATIL</t>
-        </is>
-      </c>
-      <c r="C16" s="33" t="n">
-        <v>47.8</v>
+          <t>KIMS</t>
+        </is>
+      </c>
+      <c r="C16" s="29" t="n">
+        <v>58</v>
       </c>
       <c r="D16" s="29" t="n">
-        <v>322.25</v>
-      </c>
-      <c r="E16" s="33" t="n">
-        <v>-0.26</v>
+        <v>631.05</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>0.09</v>
       </c>
       <c r="F16" s="33" t="inlineStr">
         <is>
@@ -3133,26 +3217,26 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="31" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="28" t="inlineStr">
-        <is>
-          <t>MANKIND</t>
-        </is>
-      </c>
-      <c r="C17" s="33" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>1987.8</v>
-      </c>
-      <c r="E17" s="34" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="F17" s="33" t="inlineStr">
-        <is>
-          <t>BELOW</t>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>AARTIIND</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="D17" s="36" t="n">
+        <v>418.7</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>ABOVE</t>
         </is>
       </c>
     </row>
@@ -3162,17 +3246,17 @@
       </c>
       <c r="B18" s="28" t="inlineStr">
         <is>
-          <t>SRF</t>
-        </is>
-      </c>
-      <c r="C18" s="33" t="n">
-        <v>38.5</v>
+          <t>WELCORP</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>52.2</v>
       </c>
       <c r="D18" s="29" t="n">
-        <v>2471.6</v>
+        <v>802.2</v>
       </c>
       <c r="E18" s="34" t="n">
-        <v>3.35</v>
+        <v>4.05</v>
       </c>
       <c r="F18" s="33" t="inlineStr">
         <is>
@@ -3186,17 +3270,17 @@
       </c>
       <c r="B19" s="28" t="inlineStr">
         <is>
-          <t>TANLA</t>
-        </is>
-      </c>
-      <c r="C19" s="33" t="n">
-        <v>37.1</v>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="n">
+        <v>50.7</v>
       </c>
       <c r="D19" s="29" t="n">
-        <v>410.95</v>
+        <v>3756.5</v>
       </c>
       <c r="E19" s="34" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="F19" s="33" t="inlineStr">
         <is>
@@ -3210,17 +3294,17 @@
       </c>
       <c r="B20" s="28" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="C20" s="33" t="n">
-        <v>36.9</v>
+        <v>49.5</v>
       </c>
       <c r="D20" s="29" t="n">
-        <v>433.1</v>
+        <v>1366.3</v>
       </c>
       <c r="E20" s="34" t="n">
-        <v>2.21</v>
+        <v>0.26</v>
       </c>
       <c r="F20" s="33" t="inlineStr">
         <is>
@@ -3234,17 +3318,17 @@
       </c>
       <c r="B21" s="28" t="inlineStr">
         <is>
-          <t>SAFARI</t>
+          <t>KOLTEPATIL</t>
         </is>
       </c>
       <c r="C21" s="33" t="n">
-        <v>32.6</v>
+        <v>47.8</v>
       </c>
       <c r="D21" s="29" t="n">
-        <v>1479.3</v>
+        <v>322.25</v>
       </c>
       <c r="E21" s="33" t="n">
-        <v>-0.24</v>
+        <v>-0.26</v>
       </c>
       <c r="F21" s="33" t="inlineStr">
         <is>
@@ -3258,17 +3342,17 @@
       </c>
       <c r="B22" s="28" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>MANKIND</t>
         </is>
       </c>
       <c r="C22" s="33" t="n">
-        <v>32.3</v>
+        <v>46.1</v>
       </c>
       <c r="D22" s="29" t="n">
-        <v>604.05</v>
+        <v>1987.8</v>
       </c>
       <c r="E22" s="34" t="n">
-        <v>3.71</v>
+        <v>3.13</v>
       </c>
       <c r="F22" s="33" t="inlineStr">
         <is>
@@ -3282,17 +3366,17 @@
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="C23" s="33" t="n">
-        <v>28.9</v>
+        <v>38.5</v>
       </c>
       <c r="D23" s="29" t="n">
-        <v>1334.3</v>
+        <v>2471.6</v>
       </c>
       <c r="E23" s="34" t="n">
-        <v>0.34</v>
+        <v>3.35</v>
       </c>
       <c r="F23" s="33" t="inlineStr">
         <is>
@@ -3306,17 +3390,17 @@
       </c>
       <c r="B24" s="28" t="inlineStr">
         <is>
-          <t>LXCHEM</t>
+          <t>TANLA</t>
         </is>
       </c>
       <c r="C24" s="33" t="n">
-        <v>25.1</v>
+        <v>37.1</v>
       </c>
       <c r="D24" s="29" t="n">
-        <v>118</v>
+        <v>410.95</v>
       </c>
       <c r="E24" s="34" t="n">
-        <v>4.52</v>
+        <v>2.74</v>
       </c>
       <c r="F24" s="33" t="inlineStr">
         <is>
@@ -3330,17 +3414,17 @@
       </c>
       <c r="B25" s="28" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C25" s="33" t="n">
-        <v>24.3</v>
+        <v>36.9</v>
       </c>
       <c r="D25" s="29" t="n">
-        <v>78.75</v>
+        <v>433.1</v>
       </c>
       <c r="E25" s="34" t="n">
-        <v>0.31</v>
+        <v>2.21</v>
       </c>
       <c r="F25" s="33" t="inlineStr">
         <is>
@@ -3354,17 +3438,17 @@
       </c>
       <c r="B26" s="28" t="inlineStr">
         <is>
-          <t>PDSL</t>
+          <t>SAFARI</t>
         </is>
       </c>
       <c r="C26" s="33" t="n">
-        <v>22.1</v>
+        <v>32.6</v>
       </c>
       <c r="D26" s="29" t="n">
-        <v>274.05</v>
-      </c>
-      <c r="E26" s="34" t="n">
-        <v>7.96</v>
+        <v>1479.3</v>
+      </c>
+      <c r="E26" s="33" t="n">
+        <v>-0.24</v>
       </c>
       <c r="F26" s="33" t="inlineStr">
         <is>
@@ -3378,19 +3462,139 @@
       </c>
       <c r="B27" s="28" t="inlineStr">
         <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="D27" s="29" t="n">
+        <v>604.05</v>
+      </c>
+      <c r="E27" s="34" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="28" t="inlineStr">
+        <is>
+          <t>ACC</t>
+        </is>
+      </c>
+      <c r="C28" s="33" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="D28" s="29" t="n">
+        <v>1334.3</v>
+      </c>
+      <c r="E28" s="34" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="F28" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="28" t="inlineStr">
+        <is>
+          <t>LXCHEM</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="D29" s="29" t="n">
+        <v>118</v>
+      </c>
+      <c r="E29" s="34" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="F29" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="31" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="28" t="inlineStr">
+        <is>
+          <t>BAJAJHFL</t>
+        </is>
+      </c>
+      <c r="C30" s="33" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="D30" s="29" t="n">
+        <v>78.75</v>
+      </c>
+      <c r="E30" s="34" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="F30" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>PDSL</t>
+        </is>
+      </c>
+      <c r="C31" s="33" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="D31" s="29" t="n">
+        <v>274.05</v>
+      </c>
+      <c r="E31" s="34" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="F31" s="33" t="inlineStr">
+        <is>
+          <t>BELOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="28" t="inlineStr">
+        <is>
           <t>LODHA</t>
         </is>
       </c>
-      <c r="C27" s="33" t="n">
+      <c r="C32" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D32" s="29" t="n">
         <v>726.4</v>
       </c>
-      <c r="E27" s="33" t="n">
+      <c r="E32" s="33" t="n">
         <v>-0.21</v>
       </c>
-      <c r="F27" s="33" t="inlineStr">
+      <c r="F32" s="33" t="inlineStr">
         <is>
           <t>BELOW</t>
         </is>
@@ -3412,7 +3616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3505,242 +3709,377 @@
     <row r="5" ht="16" customHeight="1">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>Mirae Asset Large &amp; Midcap Fund - Direct Plan - Growth</t>
+          <t>quant Small Cap Fund - Growth Option - Direct Plan</t>
         </is>
       </c>
       <c r="B5" s="45" t="n">
-        <v>160.17</v>
+        <v>248.64</v>
       </c>
       <c r="C5" s="46" t="n">
-        <v>3.98</v>
+        <v>-1.88</v>
       </c>
       <c r="D5" s="46" t="n">
-        <v>16.99</v>
+        <v>19.88</v>
       </c>
       <c r="E5" s="46" t="n">
-        <v>14.24</v>
+        <v>24.55</v>
       </c>
       <c r="F5" s="47" t="n">
-        <v>18.01</v>
+        <v>18.57</v>
       </c>
       <c r="G5" s="48" t="inlineStr">
         <is>
-          <t>Equity Scheme - Large &amp; Mid Cap Fund</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="49" t="inlineStr">
-        <is>
-          <t>— ETFs &amp; BeES —</t>
+          <t>Equity Scheme - Small Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="28" t="inlineStr">
+        <is>
+          <t>Franklin India Mid Cap Fund - Direct - Growth</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="n">
+        <v>2807</v>
+      </c>
+      <c r="C6" s="46" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="D6" s="46" t="n">
+        <v>20.77</v>
+      </c>
+      <c r="E6" s="46" t="n">
+        <v>16.36</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <v>15.51</v>
+      </c>
+      <c r="G6" s="48" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Mid Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>CANARA ROBECO EQUITY HYBRID FUND - DIRECT PLAN - GROWTH OPTION</t>
+        </is>
+      </c>
+      <c r="B7" s="45" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="C7" s="46" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="D7" s="46" t="n">
+        <v>13.93</v>
+      </c>
+      <c r="E7" s="46" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="F7" s="45" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="G7" s="48" t="inlineStr">
+        <is>
+          <t>Hybrid Scheme - Aggressive Hybrid Fund</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>Nifty BeES</t>
-        </is>
-      </c>
-      <c r="B8" s="29" t="n">
-        <v>259.83</v>
-      </c>
-      <c r="C8" s="35" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="D8" s="35" t="n">
-        <v>36.97</v>
-      </c>
-      <c r="E8" s="35" t="n">
-        <v>68.87</v>
-      </c>
-      <c r="F8" s="35" t="inlineStr"/>
+          <t>Axis Large Cap Fund - Direct Plan - Growth</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="n">
+        <v>64.36</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="D8" s="46" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="E8" s="46" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="F8" s="45" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="G8" s="48" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Large Cap Fund</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="28" t="inlineStr">
         <is>
-          <t>Bank BeES</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>543.04</v>
-      </c>
-      <c r="C9" s="35" t="n">
-        <v>9.51</v>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>33.08</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>63.06</v>
-      </c>
-      <c r="F9" s="35" t="inlineStr"/>
+          <t>Axis ELSS Tax Saver Fund - Direct Plan - Growth Option</t>
+        </is>
+      </c>
+      <c r="B9" s="45" t="n">
+        <v>99.61</v>
+      </c>
+      <c r="C9" s="46" t="n">
+        <v>-2.83</v>
+      </c>
+      <c r="D9" s="46" t="n">
+        <v>14.57</v>
+      </c>
+      <c r="E9" s="46" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="F9" s="45" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="G9" s="48" t="inlineStr">
+        <is>
+          <t>Equity Scheme - ELSS</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="28" t="inlineStr">
         <is>
-          <t>Gold BeES</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>115.49</v>
-      </c>
-      <c r="C10" s="35" t="n">
-        <v>57.07</v>
-      </c>
-      <c r="D10" s="35" t="n">
-        <v>143.6</v>
-      </c>
-      <c r="E10" s="35" t="n">
-        <v>196.97</v>
-      </c>
-      <c r="F10" s="35" t="inlineStr"/>
-    </row>
-    <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>Silver BeES</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>212.31</v>
-      </c>
-      <c r="C11" s="35" t="n">
-        <v>120.06</v>
-      </c>
-      <c r="D11" s="35" t="n">
-        <v>239.8</v>
-      </c>
-      <c r="E11" s="35" t="n">
-        <v>243.71</v>
-      </c>
-      <c r="F11" s="35" t="inlineStr"/>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>IT BeES</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>32.76</v>
-      </c>
-      <c r="C12" s="35" t="n">
-        <v>-16.98</v>
-      </c>
-      <c r="D12" s="35" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="E12" s="35" t="n">
-        <v>26.88</v>
-      </c>
-      <c r="F12" s="35" t="inlineStr"/>
+          <t xml:space="preserve">Taurus Flexi Cap Fund - Regular Plan - Growth </t>
+        </is>
+      </c>
+      <c r="B10" s="45" t="n">
+        <v>205.26</v>
+      </c>
+      <c r="C10" s="46" t="n">
+        <v>-3.98</v>
+      </c>
+      <c r="D10" s="46" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="E10" s="46" t="n">
+        <v>10.92</v>
+      </c>
+      <c r="F10" s="46" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="G10" s="48" t="inlineStr">
+        <is>
+          <t>Equity Scheme - Flexi Cap Fund</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="49" t="inlineStr">
+        <is>
+          <t>— ETFs &amp; BeES —</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="28" t="inlineStr">
         <is>
-          <t>Junior BeES</t>
+          <t>Nifty BeES</t>
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>672.29</v>
+        <v>259.83</v>
       </c>
       <c r="C13" s="35" t="n">
-        <v>5.78</v>
+        <v>3.03</v>
       </c>
       <c r="D13" s="35" t="n">
-        <v>70.43000000000001</v>
+        <v>36.97</v>
       </c>
       <c r="E13" s="35" t="n">
-        <v>91.26000000000001</v>
+        <v>68.87</v>
       </c>
       <c r="F13" s="35" t="inlineStr"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="28" t="inlineStr">
         <is>
-          <t>SBI Nifty ETF</t>
+          <t>Bank BeES</t>
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>245.18</v>
+        <v>543.04</v>
       </c>
       <c r="C14" s="35" t="n">
-        <v>2.96</v>
+        <v>9.51</v>
       </c>
       <c r="D14" s="35" t="n">
-        <v>36.66</v>
+        <v>33.08</v>
       </c>
       <c r="E14" s="35" t="n">
-        <v>68.17</v>
+        <v>63.06</v>
       </c>
       <c r="F14" s="35" t="inlineStr"/>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="28" t="inlineStr">
         <is>
-          <t>Momentum 100</t>
+          <t>Gold BeES</t>
         </is>
       </c>
       <c r="B15" s="29" t="n">
-        <v>58.39</v>
+        <v>115.49</v>
       </c>
       <c r="C15" s="35" t="n">
-        <v>12.2</v>
+        <v>57.07</v>
       </c>
       <c r="D15" s="35" t="n">
-        <v>83.67</v>
+        <v>143.6</v>
       </c>
       <c r="E15" s="35" t="n">
-        <v>136.78</v>
+        <v>196.97</v>
       </c>
       <c r="F15" s="35" t="inlineStr"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="28" t="inlineStr">
         <is>
-          <t>Hang Seng BeES</t>
+          <t>Silver BeES</t>
         </is>
       </c>
       <c r="B16" s="29" t="n">
-        <v>461.13</v>
+        <v>212.31</v>
       </c>
       <c r="C16" s="35" t="n">
-        <v>5.87</v>
+        <v>120.06</v>
       </c>
       <c r="D16" s="35" t="n">
-        <v>61.62</v>
+        <v>239.8</v>
       </c>
       <c r="E16" s="35" t="n">
-        <v>33.14</v>
+        <v>243.71</v>
       </c>
       <c r="F16" s="35" t="inlineStr"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
+          <t>IT BeES</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="n">
+        <v>32.76</v>
+      </c>
+      <c r="C17" s="35" t="n">
+        <v>-16.98</v>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F17" s="35" t="inlineStr"/>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Junior BeES</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="n">
+        <v>672.29</v>
+      </c>
+      <c r="C18" s="35" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="D18" s="35" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="E18" s="35" t="n">
+        <v>91.26000000000001</v>
+      </c>
+      <c r="F18" s="35" t="inlineStr"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>SBI Nifty ETF</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="n">
+        <v>245.18</v>
+      </c>
+      <c r="C19" s="35" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="D19" s="35" t="n">
+        <v>36.66</v>
+      </c>
+      <c r="E19" s="35" t="n">
+        <v>68.17</v>
+      </c>
+      <c r="F19" s="35" t="inlineStr"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Momentum 100</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="n">
+        <v>58.39</v>
+      </c>
+      <c r="C20" s="35" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="D20" s="35" t="n">
+        <v>83.67</v>
+      </c>
+      <c r="E20" s="35" t="n">
+        <v>136.78</v>
+      </c>
+      <c r="F20" s="35" t="inlineStr"/>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>Hang Seng BeES</t>
+        </is>
+      </c>
+      <c r="B21" s="29" t="n">
+        <v>461.13</v>
+      </c>
+      <c r="C21" s="35" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="D21" s="35" t="n">
+        <v>61.62</v>
+      </c>
+      <c r="E21" s="35" t="n">
+        <v>33.14</v>
+      </c>
+      <c r="F21" s="35" t="inlineStr"/>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
           <t>Bharat Bond 2032</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B22" s="29" t="n">
         <v>114.47</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C22" s="35" t="n">
         <v>15.57</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D22" s="35" t="n">
         <v>97.16</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E22" s="35" t="n">
         <v>226.96</v>
       </c>
-      <c r="F17" s="35" t="inlineStr"/>
+      <c r="F22" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
